--- a/KIT-REPRISE/18-plans-urgence.xlsx
+++ b/KIT-REPRISE/18-plans-urgence.xlsx
@@ -407,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:L1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,18 +426,30 @@
         <v>Dernière revue</v>
       </c>
       <c r="F1" t="str">
+        <v>Revue tous les (mois)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Prochaine revue</v>
+      </c>
+      <c r="H1" t="str">
+        <v>État de la revue</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Rubriques manquantes</v>
+      </c>
+      <c r="J1" t="str">
         <v>Consignes</v>
       </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
         <v>Donner l'alerte</v>
       </c>
-      <c r="H1" t="str">
+      <c r="L1" t="str">
         <v>Auteur</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -523,7 +535,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -658,7 +670,7 @@
         <v>Plans</v>
       </c>
       <c r="B7" t="str">
-        <v>Consignes</v>
+        <v>Revue tous les (mois)</v>
       </c>
       <c r="C7" t="str">
         <v>non</v>
@@ -670,7 +682,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>texte libre</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -678,7 +690,7 @@
         <v>Plans</v>
       </c>
       <c r="B8" t="str">
-        <v>Donner l'alerte</v>
+        <v>Prochaine revue</v>
       </c>
       <c r="C8" t="str">
         <v>non</v>
@@ -690,7 +702,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>texte libre</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -698,7 +710,7 @@
         <v>Plans</v>
       </c>
       <c r="B9" t="str">
-        <v>Auteur</v>
+        <v>État de la revue</v>
       </c>
       <c r="C9" t="str">
         <v>non</v>
@@ -710,35 +722,35 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>texte libre</v>
+        <v>non lue à l'import : l'application la calcule ou la reprend d'un enregistrement rattaché</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Numéros d'urgence</v>
+        <v>Plans</v>
       </c>
       <c r="B10" t="str">
-        <v>ID Plan</v>
+        <v>Rubriques manquantes</v>
       </c>
       <c r="C10" t="str">
         <v>non</v>
       </c>
       <c r="D10" t="str">
-        <v>Identifiant</v>
+        <v>Texte</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>facultatif : laissez vide pour une nouvelle ligne</v>
+        <v>non lue à l'import : l'application la calcule ou la reprend d'un enregistrement rattaché</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Numéros d'urgence</v>
+        <v>Plans</v>
       </c>
       <c r="B11" t="str">
-        <v>Site</v>
+        <v>Consignes</v>
       </c>
       <c r="C11" t="str">
         <v>non</v>
@@ -750,15 +762,15 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>non lue à l'import : l'application la calcule ou la reprend d'un enregistrement rattaché</v>
+        <v>texte libre</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Numéros d'urgence</v>
+        <v>Plans</v>
       </c>
       <c r="B12" t="str">
-        <v>Qui</v>
+        <v>Donner l'alerte</v>
       </c>
       <c r="C12" t="str">
         <v>non</v>
@@ -775,10 +787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Numéros d'urgence</v>
+        <v>Plans</v>
       </c>
       <c r="B13" t="str">
-        <v>Numéro</v>
+        <v>Auteur</v>
       </c>
       <c r="C13" t="str">
         <v>non</v>
@@ -795,7 +807,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Points de rassemblement</v>
+        <v>Numéros d'urgence</v>
       </c>
       <c r="B14" t="str">
         <v>ID Plan</v>
@@ -815,7 +827,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Points de rassemblement</v>
+        <v>Numéros d'urgence</v>
       </c>
       <c r="B15" t="str">
         <v>Site</v>
@@ -835,10 +847,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Points de rassemblement</v>
+        <v>Numéros d'urgence</v>
       </c>
       <c r="B16" t="str">
-        <v>Point de rassemblement</v>
+        <v>Qui</v>
       </c>
       <c r="C16" t="str">
         <v>non</v>
@@ -855,10 +867,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Points de rassemblement</v>
+        <v>Numéros d'urgence</v>
       </c>
       <c r="B17" t="str">
-        <v>Emplacement</v>
+        <v>Numéro</v>
       </c>
       <c r="C17" t="str">
         <v>non</v>
@@ -875,7 +887,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Personnes désignées</v>
+        <v>Points de rassemblement</v>
       </c>
       <c r="B18" t="str">
         <v>ID Plan</v>
@@ -895,7 +907,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Personnes désignées</v>
+        <v>Points de rassemblement</v>
       </c>
       <c r="B19" t="str">
         <v>Site</v>
@@ -915,10 +927,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Personnes désignées</v>
+        <v>Points de rassemblement</v>
       </c>
       <c r="B20" t="str">
-        <v>Rôle</v>
+        <v>Point de rassemblement</v>
       </c>
       <c r="C20" t="str">
         <v>non</v>
@@ -935,10 +947,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Personnes désignées</v>
+        <v>Points de rassemblement</v>
       </c>
       <c r="B21" t="str">
-        <v>Personne</v>
+        <v>Emplacement</v>
       </c>
       <c r="C21" t="str">
         <v>non</v>
@@ -958,47 +970,47 @@
         <v>Personnes désignées</v>
       </c>
       <c r="B22" t="str">
-        <v>Téléphone</v>
+        <v>ID Plan</v>
       </c>
       <c r="C22" t="str">
         <v>non</v>
       </c>
       <c r="D22" t="str">
-        <v>Texte</v>
+        <v>Identifiant</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>texte libre</v>
+        <v>facultatif : laissez vide pour une nouvelle ligne</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Moyens de secours</v>
+        <v>Personnes désignées</v>
       </c>
       <c r="B23" t="str">
-        <v>ID Plan</v>
+        <v>Site</v>
       </c>
       <c r="C23" t="str">
         <v>non</v>
       </c>
       <c r="D23" t="str">
-        <v>Identifiant</v>
+        <v>Texte</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>facultatif : laissez vide pour une nouvelle ligne</v>
+        <v>non lue à l'import : l'application la calcule ou la reprend d'un enregistrement rattaché</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Moyens de secours</v>
+        <v>Personnes désignées</v>
       </c>
       <c r="B24" t="str">
-        <v>Site</v>
+        <v>Rôle</v>
       </c>
       <c r="C24" t="str">
         <v>non</v>
@@ -1010,15 +1022,15 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>non lue à l'import : l'application la calcule ou la reprend d'un enregistrement rattaché</v>
+        <v>texte libre</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Moyens de secours</v>
+        <v>Personnes désignées</v>
       </c>
       <c r="B25" t="str">
-        <v>Type</v>
+        <v>Personne</v>
       </c>
       <c r="C25" t="str">
         <v>non</v>
@@ -1035,10 +1047,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Moyens de secours</v>
+        <v>Personnes désignées</v>
       </c>
       <c r="B26" t="str">
-        <v>Emplacement</v>
+        <v>Téléphone</v>
       </c>
       <c r="C26" t="str">
         <v>non</v>
@@ -1058,24 +1070,104 @@
         <v>Moyens de secours</v>
       </c>
       <c r="B27" t="str">
+        <v>ID Plan</v>
+      </c>
+      <c r="C27" t="str">
+        <v>non</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Identifiant</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>facultatif : laissez vide pour une nouvelle ligne</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Moyens de secours</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Site</v>
+      </c>
+      <c r="C28" t="str">
+        <v>non</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>non lue à l'import : l'application la calcule ou la reprend d'un enregistrement rattaché</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Moyens de secours</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C29" t="str">
+        <v>non</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>texte libre</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Moyens de secours</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Emplacement</v>
+      </c>
+      <c r="C30" t="str">
+        <v>non</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Texte</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>texte libre</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Moyens de secours</v>
+      </c>
+      <c r="B31" t="str">
         <v>Quantité</v>
       </c>
-      <c r="C27" t="str">
-        <v>non</v>
-      </c>
-      <c r="D27" t="str">
+      <c r="C31" t="str">
+        <v>non</v>
+      </c>
+      <c r="D31" t="str">
         <v>Nombre</v>
       </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27" t="str">
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1188,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1207,12 +1299,24 @@
         <v>Dernière revue</v>
       </c>
       <c r="F1" t="str">
+        <v>Revue tous les (mois)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Prochaine revue</v>
+      </c>
+      <c r="H1" t="str">
+        <v>État de la revue</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Rubriques manquantes</v>
+      </c>
+      <c r="J1" t="str">
         <v>Consignes</v>
       </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
         <v>Donner l'alerte</v>
       </c>
-      <c r="H1" t="str">
+      <c r="L1" t="str">
         <v>Auteur</v>
       </c>
     </row>
@@ -1232,25 +1336,37 @@
       <c r="E2" t="str">
         <v>2026-09-15</v>
       </c>
-      <c r="F2" t="str" xml:space="preserve">
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>Fréquence de revue manquante</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Fréquence de revue</v>
+      </c>
+      <c r="J2" t="str" xml:space="preserve">
         <v xml:space="preserve">Au signal d'évacuation : arrêter son activité, ne pas emporter ses affaires, fermer les portes sans les verrouiller.
 Ne pas utiliser l'ascenseur.
 Accompagner le public présent vers la sortie la plus proche.
 Rejoindre le point de rassemblement et se signaler au serre-file.
 Ne revenir dans le bâtiment qu'avec l'accord du chargé d'évacuation.</v>
       </c>
-      <c r="G2" t="str" xml:space="preserve">
+      <c r="K2" t="str" xml:space="preserve">
         <v xml:space="preserve">Actionner le déclencheur d'alarme le plus proche (un à chaque palier).
 Appeler le 18 (ou le 112) : adresse 1 place de la Mairie, entrée côté parvis ; dire ce qui se passe et combien de personnes sont concernées.
 Prévenir l'accueil (poste 100), qui informe le responsable du site.</v>
       </c>
-      <c r="H2" t="str">
+      <c r="L2" t="str">
         <v>Données de démonstration</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
